--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -43,7 +43,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="006B21A8"/>
+      <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
     <font>
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
+      <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +90,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,10 +134,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -581,135 +581,44 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Raunak Khemuka
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
 Karan Bhatia
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-56% pred | 56% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -725,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -797,135 +706,44 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Raunak Khemuka
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
 Karan Bhatia
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-56% pred | 56% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -941,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1013,135 +831,44 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Raunak Khemuka
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
 Karan Bhatia
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-56% pred | 56% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,16 +47,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,17 +70,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -134,14 +124,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -584,41 +571,41 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
+Richard D'Costa
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Raunak Khemuka
-55% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karan Bhatia
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -709,41 +696,41 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
+Richard D'Costa
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Raunak Khemuka
-55% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karan Bhatia
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -834,41 +821,41 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
+Richard D'Costa
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
 Raunak Khemuka
-55% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karan Bhatia
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,12 +46,8 @@
       <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
-    <font>
-      <color rgb="006B21A8"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,11 +72,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -126,9 +117,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -586,27 +574,6 @@
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -621,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -711,27 +678,6 @@
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -746,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -836,27 +782,6 @@
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -39,7 +39,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00555577"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -61,7 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -556,19 +556,19 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-33% pred | 0% hist
+Karan Bhatia
+34% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
@@ -660,19 +660,19 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-33% pred | 0% hist
+Karan Bhatia
+34% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
@@ -764,19 +764,19 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Richard D'Costa
-33% pred | 0% hist
+Karan Bhatia
+34% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,11 +43,20 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="006B21A8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,12 +75,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00E8D5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -115,10 +134,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -556,44 +581,135 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Cauveri Vikrant
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Raunak Khemuka
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="n"/>
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -609,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -681,44 +797,135 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Cauveri Vikrant
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Raunak Khemuka
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="n"/>
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -734,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -806,44 +1013,135 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+36% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Cauveri Vikrant
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Raunak Khemuka
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="n"/>
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,7 +39,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00555577"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -48,15 +48,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00555577"/>
       <sz val="10"/>
     </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,12 +81,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00F5F5F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -140,9 +131,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -581,35 +569,14 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
@@ -617,99 +584,71 @@
 []</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Cauveri Vikrant
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -725,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -797,35 +736,14 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
@@ -833,99 +751,71 @@
 []</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Cauveri Vikrant
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -941,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1013,35 +903,14 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
@@ -1049,99 +918,71 @@
 []</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Cauveri Vikrant
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
@@ -52,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -125,11 +134,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -497,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -513,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -526,129 +538,129 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+10-Aug</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+11-Aug</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+12-Aug</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+13-Aug</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+14-Aug</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+15-Aug</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+16-Aug</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+Mrigakshi Jaiswal
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -664,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -680,7 +692,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -693,129 +705,129 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+10-Aug</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+11-Aug</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+12-Aug</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+13-Aug</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+14-Aug</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+15-Aug</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+16-Aug</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+Mrigakshi Jaiswal
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -831,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -847,7 +859,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -860,129 +872,129 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+10-Aug</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+11-Aug</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+12-Aug</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+13-Aug</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+14-Aug</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+15-Aug</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+16-Aug</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Raunak Khemuka
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+Mrigakshi Jaiswal
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,10 +134,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -581,86 +581,93 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+Anmol Sharma
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Richard D'Costa
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Anmol Sharma
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+Karanvir Bhatia
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -748,86 +755,93 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+Anmol Sharma
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Richard D'Costa
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Anmol Sharma
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+Karanvir Bhatia
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -915,86 +929,93 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
+Anmol Sharma
+66% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+82% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Richard D'Costa
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Anmol Sharma
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+Karanvir Bhatia
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+25% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -39,7 +39,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00555577"/>
       <sz val="10"/>
     </font>
     <font>
@@ -52,7 +52,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00555577"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -70,12 +70,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00F5F5F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F8"/>
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,13 +134,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -581,82 +581,82 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Anmol Sharma
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+Raunak Khemuka
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pranjali Jain
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Richard D'Costa
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -664,10 +664,31 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Vivaran Dhasmana
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -683,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -755,82 +776,82 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Anmol Sharma
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+Raunak Khemuka
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pranjali Jain
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Richard D'Costa
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -838,10 +859,31 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Vivaran Dhasmana
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -857,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -929,82 +971,82 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Mat 57
-Anmol Sharma
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+Raunak Khemuka
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pranjali Jain
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Richard D'Costa
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -1012,10 +1054,31 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Vivaran Dhasmana
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
